--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_010/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_010/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,6 +364,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -540,6 +560,41 @@
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1291,17 +1346,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>LEO-ABRKT-02 Antenna Support Arm FEA</t>
+          <t>LEO Antenna Bracket FEA (LEO-ABRKT-02)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Finite element structural analysis of LEO S-band antenna support arm under ascent, vibration, and thermal loads</t>
+          <t>Finite element analysis of S-band antenna support arm for ascent loads, random vibration, and on-orbit thermal/preload conditions</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Abaqus/Standard FEA of aluminum (7075-T7351) support arm carrying S-band antenna through worst-case ascent loads (1.8 g axial, 0.8 g lateral), random vibration PSD (20–2000 Hz), and on-orbit thermal swing (-80°C to +60°C) with preload retention. Results used to establish structural margins at CDR.</t>
+          <t>Abaqus/Standard 2023 HF1 FEA of the aluminum (7075-T7351) support arm and clevis assembly carried on a LEO spacecraft deck. The model is used to assess structural margins under worst-case ascent inertial loads (1.8 g axial, 0.8 g lateral), random vibration PSD (20–2000 Hz), and thermal cycling (-80 C to +60 C) with bolt preload retention. Results feed CDR margin tables and drive design acceptance decisions.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1339,9 +1394,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1402,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1525,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>System-level structural and dynamic requirements for the S-band antenna support arm, including load envelope, minimum frequency keep-out (150 Hz), and factor-of-safety targets</t>
+          <t>System-level structural requirements for the S-band antenna support arm covering ascent loads, vibration, thermal swing, and preload retention; define the load cases the FEA must bound and the factors of safety the model must demonstrate</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1492,12 +1547,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Structural Margin Adequacy Requirement</t>
+          <t>First-mode frequency keep-out (≥150 Hz)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Factor of safety above yield must remain adequate under as-built geometry, realistic joint contact, and temperature-dependent material properties for CDR acceptance</t>
+          <t>Dynamics requirement that the first bending mode of the support arm must be at or above 150 Hz to avoid coupling with the launch vehicle environment; driven by DRN-0247</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1564,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF1 FEA Model (v19)</t>
+          <t>Abaqus/Standard 2023 HF1 FEA model (v19)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Finite element model of arm, clevis, and two-bolt deck interface with surface interaction contact, bolt pretension elements, and geometry from CAD rev H STEP file</t>
+          <t>Finite element model of the LEO-ABRKT-02 support arm, clevis, and two-bolt deck interface; includes surface interaction with friction, bolt pretension elements, and linear elastic material for 7075-T7351</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1581,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>DRN-0247 Dynamics Release and MT-031 Metrology Report</t>
+          <t>DRN-0247 loads and PSD release</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Loads release (gravity vectors, vibe PSD) from Dynamics group and as-built dimensional metrology showing inner fillet 6.2–6.6 mm vs. 8 mm nominal</t>
+          <t>Dynamics team release document providing the ascent gravity vectors and random vibration power spectral density used as model inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Metrology report MT-031</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>As-built dimensional inspection report for the development unit noting the inner fillet radius is 6.2–6.6 mm rather than the nominal 8 mm modeled in v19</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1968,7 +2040,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study — Linear Static Ascent Case</t>
+          <t>Industry benchmark comparison (solver verification)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1983,12 +2055,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three meshes (1.8M, 3.9M, 7.4M DOF) run for linear static ascent; peak von Mises stress at knee and tip deflection monitored across refinement levels</t>
+          <t>Abaqus/Standard results compared against NASA Cranfield lug and bolted lap-plate benchmark problems to check stress contours and joint slip-onset loads</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / asymptotic convergence criterion</t>
+          <t>Published reference solutions for two standard benchmarks</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2003,19 +2075,19 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Peak von Mises change from coarsest to finest mesh ~1.8% (286 to 281 MPa); tip deflection variation &lt;1%</t>
+          <t>4–7% difference from reference solutions</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Solver Benchmark Verification</t>
+          <t>Mesh convergence study — linear static ascent case</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2025,12 +2097,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard results compared against two industry benchmark problems: NASA Cranfield lug and a bolted lap plate, assessing stress contours and joint slip-onset loads</t>
+          <t>Three mesh densities (1.8M, 3.9M, 7.4M DOF) run for the bonded-contact linear static case; peak von Mises at the knee and tip deflection monitored for convergence</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Published reference solutions (NASA Cranfield lug benchmark, bolted lap plate benchmark)</t>
+          <t>Self-convergence across mesh levels; Richardson-extrapolation-style stabilization check</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2040,19 +2112,19 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>4–7% difference from reference solutions</t>
+          <t>Peak von Mises change ~1.8% (286 to 281 MPa) from coarsest to finest; tip deflection &lt;1% variation</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Cross-Solver Tool-to-Tool Comparison</t>
+          <t>Contact sensitivity — bonded vs. friction/pretension joint</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2062,12 +2134,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Results from primary Abaqus run repeated on a second solver; differences reported globally and locally</t>
+          <t>Comparison of knee stress between v17 (tied constraints) and v19 (surface interaction with friction µ=0.2 and 5.5 kN bolt pretension) to assess joint modeling influence</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Second independent solver run</t>
+          <t>v17 tied-constraint baseline results</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2077,7 +2149,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>&lt;3% at arm midspan; 9–12% near bolt head contact regions; secondary solver used single precision vs. double precision primary</t>
+          <t>11–14% increase in knee stress when contact is enabled (text erroneously claims &lt;3%)</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2089,7 +2161,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Joint Contact Sensitivity Study</t>
+          <t>Tool-to-tool cross-check (Abaqus vs. backup solver)</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2099,12 +2171,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Comparison of tied/bonded constraint (v17) versus surface interaction with friction and bolt pretension (v19) on peak knee stress</t>
+          <t>Results from primary Abaqus run compared to a second solver for arm midspan stress and bolt-head contact pressure regions; precision settings differed between runs</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>v17 bonded contact baseline</t>
+          <t>Backup solver results</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2114,7 +2186,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Text claims &lt;3% effect; sensitivity sheet shows 11–14% increase in knee stress with contact enabled — inconsistent</t>
+          <t>3% at midspan; 9–12% near bolt head in high-gradient regions</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2126,7 +2198,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Pull Test Coupon Correlation (AlSi10Mg Surrogate)</t>
+          <t>Flexible deck sensitivity (NX Nastran superelement swap)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2136,12 +2208,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Physical pull tests performed on AlSi10Mg printed coupons used as geometric surrogate for 7075-T7351 arm; correlation of structural response claimed at 5%</t>
+          <t>Fixed-deck boundary condition replaced with a CFRP sandwich superelement to assess stiffness sensitivity; tip displacement and first modal frequency monitored</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Physical test data from AlSi10Mg surrogate coupons</t>
+          <t>Fully-fixed baseline case</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2151,12 +2223,49 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>~5% correlation claimed; surrogate alloy differs from flight alloy — not like-for-like</t>
+          <t>Tip displacement increase 0.4–0.6 mm; first mode reduction ~7%</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Inconclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>As-built fillet radius margin sensitivity</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Side calculation assessing the effect of the as-built fillet radius (6.2–6.6 mm per MT-031) versus nominal (8 mm) on peak stress and factor of safety above yield</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Nominal-geometry FEA margin table (FOS = 1.42)</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>~14% stress increase; FOS reduces from ~1.42 to ~1.25 without temperature effects</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2414,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA, version control, and regression testing</t>
+          <t>Solver must be a commercially supported, versioned code with documented verification and regression testing applicable to structural contact and modal analysis</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF1 is a commercially qualified solver with implied QA processes. However, the cross-solver comparison reveals single-precision vs. double-precision inconsistency between runs, and the "&lt;3% difference" claim is contradicted by 9–12% local deviations near bolt heads. No explicit reference to Abaqus QA certification documentation, regression test suite, or formal SQA plan is provided in the evidence. Achieved level is basic at best given the unresolved precision mismatch.</t>
+          <t>The report identifies Abaqus/Standard 2023 HF1 by version, implying a commercial release with vendor QA. Two industry benchmark comparisons (NASA Cranfield lug, bolted lap plate) are noted with 4–7% agreement. However, no explicit reference to vendor qualification documentation, regression test suite, or ISO/AS9100 process evidence is provided. The secondary solver run introduces inconsistency (single vs. double precision) that undermines confidence in controlled tool usage.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2335,16 +2444,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Comparison to analytical or established benchmark solutions within acceptable tolerance</t>
+          <t>Code must be verified against analytical or benchmark solutions for the relevant physics (linear statics, contact, modal, random vibration)</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Two industry benchmark problems (NASA Cranfield lug, bolted lap plate) were exercised with stress contours and joint slip-onset loads within 4–7% of reference solutions. This constitutes adequate numerical code verification for the linear structural regime. The benchmarks are relevant to the joint and lug geometry of interest, though no manufactured solution or formal order-of-accuracy study is documented.</t>
+          <t>Benchmark comparisons to NASA Cranfield lug and bolted lap-plate reference solutions show 4–7% agreement, which provides partial verification for linear static with contact. No verification evidence is cited for the modal or random vibration cases. The tool-to-tool delta reaches 9–12% near bolt heads, and the precision discrepancy (single vs. double) between primary and backup runs weakens the cross-check value.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2373,12 +2482,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated for all critical load cases including vibration; GCI or equivalent metric reported</t>
+          <t>Mesh convergence must be demonstrated for all load cases reported in the margin tables, with quantified change in QoIs across refinement levels</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>A three-mesh convergence study was performed for the linear static ascent case, showing ~1.8% stress change and &lt;1% deflection change across refinement levels — reasonable for that case. However, the vibe analysis was run on the coarsest mesh due to time constraints, so the convergence result does not apply to vibe stresses. Additionally, final v19 mesh uses 0.8 mm minimum (not 0.5 mm as claimed) with curvature control disabled on two ribs, contradicting the convergence narrative. Incomplete coverage lowers the achieved level.</t>
+          <t>A three-level mesh convergence study (1.8M–7.4M DOF) was performed for the linear static bonded-contact case, showing ~1.8% peak stress change and &lt;1% tip deflection change at the finest level. However, the v19 deck records 0.8 mm minimum element size (not the stated 0.5 mm) with curvature control disabled on two ribs, creating inconsistency with the convergence claim. Critically, the vibe case used the coarsest mesh for schedule reasons, so the 1.8% stabilization figure does not apply to that case. No GCI or Richardson extrapolation was reported.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2400,19 +2509,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Convergence monitoring documented; residual targets and iteration counts reported</t>
+          <t>Iterative solver convergence residuals and contact iteration convergence should be documented for all run cases</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>No explicit documentation of residual convergence targets, iteration counts, or solver tolerance settings is provided in the evidence memo. The cross-solver comparison partially addresses solver behavior but is undermined by the single- vs. double-precision inconsistency. Implicit in the commercial solver use that defaults are applied, but no formal reporting of solver convergence criteria is evident.</t>
+          <t>The report does not explicitly document residual targets, convergence monitoring, or iteration counts for any run case. The tool-to-tool comparison partially serves as a surrogate check but is undermined by the single-vs.-double precision inconsistency and the 9–12% discrepancy in high-gradient regions. No solver log excerpts or residual plots are referenced.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2441,12 +2550,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup, boundary conditions, mesh quality, and load application by a separate qualified reviewer</t>
+          <t>An independent reviewer must verify boundary conditions, load application, contact definitions, and material assignments before results are used in margin tables</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>The memo explicitly states that the "independent check by Structures Team B" has the assessor's own initials for both setup and check due to Team B's unavailability. This means no true independent review was conducted. Multiple setup errors or inconsistencies are identified: load sign coverage incomplete (+Y/+Z only for static, not -Y/-Z), conflicting material models (elastic-plastic referenced in text but only linear elasticity in v19 .inp file), and conflict between claimed and actual mesh sizing. These collectively indicate elevated use error risk with no independent verification catch.</t>
+          <t>The report explicitly flags that the "independent check by Structures Team B" was not performed independently — the assessor's initials appear for both the setup and the check role due to Team B's unavailability. Multiple setup inconsistencies are documented: contact model in v19 differs from what the text describes; material model (elastic-plastic vs. linear elastic) is inconsistent between the memo and the vault .inp file; fixed-deck assumption carried over from PDR without update; load sign coverage incomplete for lateral cases. These are direct evidence of elevated use-error risk with no independent check in place.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2475,12 +2584,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and constitutive models justified for the physics regime; known limitations documented</t>
+          <t>Governing equations, contact formulation, and material constitutive model must be justified for the operating regime and known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>The memo references linear elasticity as the operative model, with an elastic-plastic tangent modulus check claimed in text but absent from the v19 input file — creating ambiguity about which model underlies the reported FOS. Temperature-dependent modulus effects are acknowledged (MMPDS footnote cites +6% at -80°C) but not implemented; constant E and ν are used throughout. The fixed-deck boundary condition is carried from PDR and is known to be non-representative of the flexible CFRP sandwich. Model form limitations are identified but not resolved, and the governing model state is inconsistent between documentation and the actual input file.</t>
+          <t>The report documents use of linear elasticity in the vault v19 .inp, but an elastic-plastic check with 1.2 GPa tangent modulus is mentioned in the memo text — it is unclear which underlies the reported FOS, a significant model-form uncertainty. The joint model changed from tied to friction/pretension between v17 and v19 without consistent propagation across all load cases. The fixed-deck assumption is acknowledged as a limitation but has not been corrected. Temperature-dependent elastic modulus is noted as omitted despite MMPDS guidance for the -80 C case.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2509,12 +2618,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, geometry, and boundary conditions traceable to measurements or standards; input uncertainties characterized</t>
+          <t>Material properties, geometry, preload values, and load inputs must be traceable to measurements or qualified sources and uncertainty must be characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Loads trace to DRN-0247 and requirements SYS-ANT-REQ-112–118, providing some traceability. Material properties cite 7075-T7351 from MMPDS (room temperature), but temperature dependence is not implemented. As-built geometry from MT-031 shows 6.2–6.6 mm fillet vs. 8 mm nominal — a known 14% stress impact — yet the margin table uses nominal geometry. Bolt friction coefficient µ=0.2 is specified but source/measurement is not cited. No formal input uncertainty characterization or sensitivity study covering the full input space is documented. Multiple inputs are inconsistent between documentation and executed model.</t>
+          <t>Load inputs trace to DRN-0247 and requirements SYS-ANT-REQ-112–118, providing adequate traceability for that subset. Material properties cite MMPDS for 7075-T7351 room-temperature values (503 MPa yield, 71 GPa modulus) but the temperature correction (+6% at -80 C) is noted and then omitted from the model. The as-built fillet geometry (6.2–6.6 mm per MT-031) differs from the nominal 8 mm used in the model, with a documented 14% stress impact. Friction coefficient (µ = 0.2) and bolt pretension (5.5 kN) are stated but without source traceability. No input uncertainty characterization or sensitivity matrix is provided.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2543,12 +2652,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles representative of flight hardware in material and geometry; sample characterization documented</t>
+          <t>Physical test articles used for correlation should be production-representative in alloy, geometry, and manufacturing process</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Pull test coupons used for correlation are AlSi10Mg printed material, explicitly identified as a "geometric surrogate" for the 7075-T7351 flight alloy. This is not a like-for-like test sample. No flight-alloy test articles are documented. Number of coupons, statistical characterization, and production-representativeness are not reported. The surrogate approach fundamentally limits the evidential value of the test data for validating the flight hardware model.</t>
+          <t>Pull test coupons used as a geometric surrogate were AlSi10Mg (printed material), not 7075-T7351 as flown. The report acknowledges this is not a like-for-like alloy comparison. The number of coupons, statistical characterization, and representativeness of the manufacturing process are not described. No evidence of test articles matching the as-built fillet geometry noted in MT-031.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2577,12 +2686,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions controlled and measured with calibrated instruments; measurement uncertainties reported; relevant test standard referenced</t>
+          <t>Test conditions must be documented with calibrated instruments, controlled environment, and traceable measurement uncertainty</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>No documentation of test setup, instrument calibration, environmental controls, or measurement uncertainty is provided for the pull tests. No reference to ASTM, ISO, or other applicable test standard is made. The memo characterizes test results only as "correlation within 5%" without any supporting test report details. Evidence is minimal.</t>
+          <t>The correlation data referenced is from pull tests on AlSi10Mg surrogate coupons. No description of test setup, environmental controls, instrumentation calibration, or measurement uncertainty is provided in the report. Test standards (e.g., ASTM E8 for tensile testing) are not cited. The evidence base for test conditions is essentially absent in this document.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2611,12 +2720,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs demonstrably match experimental test conditions; boundary condition and load equivalency documented</t>
+          <t>Model boundary conditions and material inputs must be demonstrably matched to the physical test or operational conditions used for comparison</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>The surrogate coupon test used a different alloy (AlSi10Mg vs. 7075-T7351), so input parameter equivalency between test and model is not achieved. No formal comparison of test boundary conditions to model boundary conditions is documented. The fixed-deck assumption used in the model does not reflect the measured structural compliance found in the NX Nastran superelement check. Multiple input parameters (fillet radius, material, joint contact) differ between model and test or between model versions. Equivalency is not established.</t>
+          <t>The surrogate coupon test used a different alloy (AlSi10Mg vs. 7075-T7351), so input parameter equivalency between model and test is not established for the primary material. The model uses nominal 8 mm fillet geometry while the test hardware has 6.2–6.6 mm as-built fillets (MT-031). The fixed-deck boundary condition does not match the actual CFRP sandwich deck stiffness. Temperature-dependent properties are omitted from the model despite known operating range. There is no documented comparison of model inputs to test or operational conditions.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2645,12 +2754,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to experimental measurements at relevant output locations; uncertainty bands reported</t>
+          <t>Predicted stress, displacement, and modal frequency must be compared quantitatively to experimental measurements with uncertainty bands; agreement thresholds must be defined and evaluated</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>A 5% correlation figure is claimed between model and surrogate coupon pull tests, but the alloy mismatch undermines its validity. The cross-solver comparison provides some output comparison but is compromised by precision inconsistency (9–12% local deviation near bolts). Mesh convergence provides internal model consistency checks. No uncertainty bands, confidence intervals, or statistical validation metrics are reported. The joint sensitivity discrepancy (text: &lt;3%; sheet: 11–14%) indicates output comparison reliability is questionable. Partial evidence exists but with significant unresolved contradictions.</t>
+          <t>The report provides benchmark comparisons (4–7% error vs. reference solutions) and a tool-to-tool comparison (3% at midspan, 9–12% at bolt head). The 5% agreement claim for the AlSi10Mg pull test correlation is stated but not substantiated with a like-for-like alloy. No experimental validation of stress or displacement against hardware test data for the actual 7075 arm is presented. No uncertainty bands are reported on model outputs or test measurements. The internal inconsistencies (contact sensitivity 11–14%, fillet effect 14%) further undermine the output comparison basis for the margin tables.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2679,12 +2788,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (peak stress, FOS, first modal frequency, tip deflection) directly address the safety and performance requirements and are both computationally and experimentally accessible</t>
+          <t>Model outputs (peak von Mises stress, tip deflection, first modal frequency, factor of safety) must directly address the structural margin requirements in SYS-ANT-REQ-112–118</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The QoIs are clearly identified and directly relevant: peak von Mises stress at the knee (yield margin), factor of safety above yield, first bending mode frequency (150 Hz keep-out), tip deflection, and preload retention under thermal cycling. These map directly to SYS-ANT-REQ-112–118. The QoIs are standard structural metrics computable in FEA and measurable in test. The relevance of the QoIs themselves is not in question; the issues lie in the quality of prediction, not the choice of output.</t>
+          <t>The QoIs selected — peak von Mises stress at the knee, tip deflection, first bending mode frequency, and factor of safety above yield — are directly relevant to the structural requirements and CDR decision. The first bending mode (182 Hz vs. 150 Hz keep-out) is a directly measurable and decision-relevant output. Stress-based FOS maps to the yield margin requirement. The QoIs are appropriate and consistently tracked across the study, even if the numerical values carry unresolved uncertainty.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2713,12 +2822,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation activities cover the same geometry, material, load regime, and environmental conditions as the intended COU (ascent, vibe, thermal); gaps documented and bounded</t>
+          <t>Validation activities must cover the same alloy, geometry, joint configuration, boundary conditions, load cases, and operating temperature range as the actual COU</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>The primary validation activity (pull test correlation) uses a different alloy and does not cover the vibration or thermal load cases. No thermal validation is documented. The vibe case was run on an unverified coarse mesh. The benchmark problems (Cranfield lug, bolted lap plate) are relevant to joint behavior in general but are not flight-like in geometry or material. The flexible deck compliance is not represented in validated configurations. The gap between validation conditions and the actual COU (flight loads, flight alloy, as-built geometry, flexible boundary) is large and not formally bounded. Validation coverage of the COU envelope is minimal.</t>
+          <t>The validation activities fall significantly short of COU coverage. The only physical test correlation uses AlSi10Mg surrogate coupons rather than 7075-T7351 flight alloy. The as-built geometry (6.2–6.6 mm fillet) is not represented in any validated configuration. The flexible CFRP deck boundary condition is not included in the baseline validated model. Temperature-dependent material response is not validated. Sign-reversed lateral load cases are missing from the static run set. The vibe case uses a coarser mesh than the converged static case, and no experimental modal or vibration test data is referenced for comparison.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2903,7 +3012,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The FEA of LEO-ABRKT-02 in its current state (v19) cannot be accepted as a credible basis for CDR structural margins. Multiple critical deficiencies are identified: (1) the joint contact model produces 11–14% higher knee stress than the bonded model, yet the margin tables have not been consistently updated; (2) the as-built fillet radius of 6.2–6.6 mm (vs. 8 mm nominal) reduces the reported 1.42 FOS to approximately 1.25 before thermal effects are applied; (3) temperature-dependent material properties from MMPDS are acknowledged but not implemented; (4) the vibe analysis was run on an unverified coarse mesh; (5) the independent review was not actually independent; (6) the governing material model (linear vs. elastic-plastic) is inconsistent between documentation and the v19 input file; and (7) load sign coverage is incomplete for lateral static cases. These issues cumulatively make the stated factors of safety optimistic and the model not suitable for acceptance. Results should be labeled provisional. Acceptance pending: consistent contact model propagated through all load cases, mesh refinement applied to vibe, temperature-dependent properties implemented or bounded, as-built fillet geometry used in margin table, true independent peer review, and corrected tool-to-tool comparison statement.</t>
+          <t>The FEA model (v19) is not accepted for use in CDR margin tables in its current state. Multiple unresolved inconsistencies collectively undermine the reliability of the reported factors of safety: (1) the joint contact model produces 11–14% higher knee stress than the bonded baseline, yet the text reports &lt;3% sensitivity — the discrepancy is unresolved and the margin table source is ambiguous; (2) the as-built fillet radius (6.2–6.6 mm per MT-031) reduces the FOS from ~1.42 to ~1.25 before temperature effects are applied, potentially approaching the acceptance threshold; (3) the material model in the vault .inp is linear elastic, inconsistent with the elastic-plastic check described in the memo — it is unknown which underlies the reported FOS; (4) the fixed-deck assumption is acknowledged to reduce the first mode by ~7%, yet the current results reference the stiffer baseline; (5) the vibe case was run on the coarsest mesh, so mesh convergence is not demonstrated for that load case; (6) no independent review was performed — the assessor signed both setup and check roles; (7) the physical test correlation uses a different alloy (AlSi10Mg vs. 7075-T7351), providing no valid like-for-like validation. Acceptance is contingent on: locking the joint model and re-running all load cases consistently; applying as-built fillet geometry in the margin tables; resolving the material model discrepancy and applying temperature-dependent properties; replacing the fixed-deck with a flexible CFRP submodel for modal and lateral cases; re-running vibe on the refined mesh; completing sign-reversed lateral load cases; and obtaining a genuine independent peer review from Team B.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
